--- a/output/pdf_financials_xlsx/RRI.xlsx
+++ b/output/pdf_financials_xlsx/RRI.xlsx
@@ -5984,49 +5984,49 @@
         <v>0.6204769999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.938541</v>
+        <v>0.953385</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.531874</v>
+        <v>1.517861</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.049739</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.366436</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.588089</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.712413</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.780005</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.046457</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.194415</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.292422</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.670485</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.770448</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.852459</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.983869</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.903469</v>
       </c>
     </row>
     <row r="93">
@@ -10011,7 +10011,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11205,7 +11209,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12710,7 +12718,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -13009,7 +13021,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14434,7 +14450,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15426,7 +15446,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -16434,7 +16458,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RRI.xlsx
+++ b/output/pdf_financials_xlsx/RRI.xlsx
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.09732200000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.07037</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.026572</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.07919900000000001</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.102949</v>
@@ -1065,19 +1065,19 @@
         <v>-0.042591</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015094</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.065473</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.273519</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.302637</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.163329</v>
       </c>
     </row>
     <row r="13">
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.047479</v>
+        <v>-1.144801</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.694217</v>
+        <v>-1.764587</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.200563</v>
+        <v>-1.227135</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.283664</v>
+        <v>0.204465</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-4.368924</v>
@@ -2027,19 +2027,19 @@
         <v>-1.26824</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.734132</v>
+        <v>0.7492259999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.207586</v>
+        <v>-0.142113</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.395191</v>
+        <v>-0.121672</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.595109</v>
+        <v>-1.292472</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>2.528105</v>
+        <v>2.691434</v>
       </c>
     </row>
     <row r="28">
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.047479</v>
+        <v>-1.144801</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.694217</v>
+        <v>-1.764587</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.200563</v>
+        <v>-1.227135</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.325085</v>
+        <v>0.245886</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-4.297025</v>
@@ -2143,19 +2143,19 @@
         <v>-1.246539</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.810075</v>
+        <v>0.825169</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.144433</v>
+        <v>-0.07896</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.340425</v>
+        <v>-0.06690599999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.553789</v>
+        <v>-1.251152</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>2.556061</v>
+        <v>2.71939</v>
       </c>
     </row>
     <row r="30">
@@ -2414,28 +2414,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.174127</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.081723</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.014845</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.554997</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.829521</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.226761</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.360889</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.781941</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.690714</v>
@@ -2530,28 +2530,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>3.767243</v>
+        <v>3.94137</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>3.592446</v>
+        <v>3.674169</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.957929</v>
+        <v>2.972774</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>11.744585</v>
+        <v>12.299582</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>7.167266</v>
+        <v>8.996786999999999</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4.264972</v>
+        <v>6.491733</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.916722</v>
+        <v>6.277611</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.477289</v>
+        <v>4.25923</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.061198</v>
@@ -3226,28 +3226,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.347581</v>
+        <v>0.173454</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.243057</v>
+        <v>0.161334</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.240511</v>
+        <v>0.225666</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.955817</v>
+        <v>0.40082</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.695344</v>
+        <v>0.865823</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.570867</v>
+        <v>0.344106</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.506428</v>
+        <v>0.145539</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.844149</v>
+        <v>0.062208</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.054853</v>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -41698,7 +41698,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -54773,7 +54773,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E470" s="5" t="n">
